--- a/data/nzd0259/nzd0259.xlsx
+++ b/data/nzd0259/nzd0259.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U349"/>
+  <dimension ref="A1:U352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24436,7 +24436,7 @@
         <v>308.06</v>
       </c>
       <c r="F349" t="n">
-        <v>312.77</v>
+        <v>305.87</v>
       </c>
       <c r="G349" t="n">
         <v>322.47</v>
@@ -24478,9 +24478,216 @@
         <v>327.63</v>
       </c>
       <c r="T349" t="n">
-        <v>328.19</v>
+        <v>317.33</v>
       </c>
       <c r="U349" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>347.75</v>
+      </c>
+      <c r="C350" t="n">
+        <v>320.92</v>
+      </c>
+      <c r="D350" t="n">
+        <v>307.27</v>
+      </c>
+      <c r="E350" t="n">
+        <v>305.34</v>
+      </c>
+      <c r="F350" t="n">
+        <v>299.8</v>
+      </c>
+      <c r="G350" t="n">
+        <v>325.28</v>
+      </c>
+      <c r="H350" t="n">
+        <v>329.52</v>
+      </c>
+      <c r="I350" t="n">
+        <v>334.75</v>
+      </c>
+      <c r="J350" t="n">
+        <v>341.67</v>
+      </c>
+      <c r="K350" t="n">
+        <v>348.29</v>
+      </c>
+      <c r="L350" t="n">
+        <v>348.27</v>
+      </c>
+      <c r="M350" t="n">
+        <v>350.06</v>
+      </c>
+      <c r="N350" t="n">
+        <v>360</v>
+      </c>
+      <c r="O350" t="n">
+        <v>356.21</v>
+      </c>
+      <c r="P350" t="n">
+        <v>356.68</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>364.51</v>
+      </c>
+      <c r="R350" t="n">
+        <v>362.56</v>
+      </c>
+      <c r="S350" t="n">
+        <v>318.09</v>
+      </c>
+      <c r="T350" t="n">
+        <v>309.15</v>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>345.92</v>
+      </c>
+      <c r="C351" t="n">
+        <v>317.21</v>
+      </c>
+      <c r="D351" t="n">
+        <v>302.9</v>
+      </c>
+      <c r="E351" t="n">
+        <v>302.12</v>
+      </c>
+      <c r="F351" t="n">
+        <v>291.98</v>
+      </c>
+      <c r="G351" t="n">
+        <v>322.57</v>
+      </c>
+      <c r="H351" t="n">
+        <v>330.66</v>
+      </c>
+      <c r="I351" t="n">
+        <v>336.13</v>
+      </c>
+      <c r="J351" t="n">
+        <v>341.86</v>
+      </c>
+      <c r="K351" t="n">
+        <v>345.06</v>
+      </c>
+      <c r="L351" t="n">
+        <v>344.62</v>
+      </c>
+      <c r="M351" t="n">
+        <v>347.94</v>
+      </c>
+      <c r="N351" t="n">
+        <v>357.37</v>
+      </c>
+      <c r="O351" t="n">
+        <v>355.85</v>
+      </c>
+      <c r="P351" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>365.4</v>
+      </c>
+      <c r="R351" t="n">
+        <v>362.21</v>
+      </c>
+      <c r="S351" t="n">
+        <v>305.09</v>
+      </c>
+      <c r="T351" t="n">
+        <v>296.66</v>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:12+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>346.13</v>
+      </c>
+      <c r="C352" t="n">
+        <v>316.96</v>
+      </c>
+      <c r="D352" t="n">
+        <v>301.4</v>
+      </c>
+      <c r="E352" t="n">
+        <v>302.46</v>
+      </c>
+      <c r="F352" t="n">
+        <v>290.23</v>
+      </c>
+      <c r="G352" t="n">
+        <v>321.7</v>
+      </c>
+      <c r="H352" t="n">
+        <v>330.28</v>
+      </c>
+      <c r="I352" t="n">
+        <v>336.66</v>
+      </c>
+      <c r="J352" t="n">
+        <v>342.91</v>
+      </c>
+      <c r="K352" t="n">
+        <v>344.12</v>
+      </c>
+      <c r="L352" t="n">
+        <v>343.51</v>
+      </c>
+      <c r="M352" t="n">
+        <v>348.16</v>
+      </c>
+      <c r="N352" t="n">
+        <v>357.2</v>
+      </c>
+      <c r="O352" t="n">
+        <v>356.46</v>
+      </c>
+      <c r="P352" t="n">
+        <v>357.28</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>365.27</v>
+      </c>
+      <c r="R352" t="n">
+        <v>361.48</v>
+      </c>
+      <c r="S352" t="n">
+        <v>301.05</v>
+      </c>
+      <c r="T352" t="n">
+        <v>293.98</v>
+      </c>
+      <c r="U352" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24497,7 +24704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B358"/>
+  <dimension ref="A1:B361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28080,6 +28287,36 @@
       </c>
       <c r="B358" t="n">
         <v>-0.78</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>1.01</v>
       </c>
     </row>
   </sheetData>
@@ -28248,28 +28485,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0679522393755652</v>
+        <v>-0.06650894294160994</v>
       </c>
       <c r="J2" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K2" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007687828778656702</v>
+        <v>0.007487008001907269</v>
       </c>
       <c r="M2" t="n">
-        <v>3.983231858402356</v>
+        <v>3.956936583297106</v>
       </c>
       <c r="N2" t="n">
-        <v>33.10464911790186</v>
+        <v>32.83356277660118</v>
       </c>
       <c r="O2" t="n">
-        <v>5.753663973321857</v>
+        <v>5.730057833617492</v>
       </c>
       <c r="P2" t="n">
-        <v>347.4952805877093</v>
+        <v>347.4796852215981</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -28330,28 +28567,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04623855501705622</v>
+        <v>-0.05064519461103183</v>
       </c>
       <c r="J3" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K3" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004477558158650918</v>
+        <v>0.005437486656034829</v>
       </c>
       <c r="M3" t="n">
-        <v>4.211928868633591</v>
+        <v>4.196570535289176</v>
       </c>
       <c r="N3" t="n">
-        <v>26.39663366132994</v>
+        <v>26.26358199936946</v>
       </c>
       <c r="O3" t="n">
-        <v>5.137765434634978</v>
+        <v>5.124800678989327</v>
       </c>
       <c r="P3" t="n">
-        <v>322.3740876652246</v>
+        <v>322.4217181706482</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -28412,28 +28649,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02317313725990815</v>
+        <v>0.02405919838711195</v>
       </c>
       <c r="J4" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K4" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005320069286702811</v>
+        <v>0.0005824965417772221</v>
       </c>
       <c r="M4" t="n">
-        <v>6.012841125185623</v>
+        <v>5.979926042823185</v>
       </c>
       <c r="N4" t="n">
-        <v>56.0210815810623</v>
+        <v>55.5980415528995</v>
       </c>
       <c r="O4" t="n">
-        <v>7.484723213390212</v>
+        <v>7.456409427660172</v>
       </c>
       <c r="P4" t="n">
-        <v>302.6752240030642</v>
+        <v>302.6656869230369</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -28494,28 +28731,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2619676197629935</v>
+        <v>0.2570187788056412</v>
       </c>
       <c r="J5" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K5" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07881333311168703</v>
+        <v>0.07710860525317353</v>
       </c>
       <c r="M5" t="n">
-        <v>4.741464117621603</v>
+        <v>4.727730979539018</v>
       </c>
       <c r="N5" t="n">
-        <v>44.54237764847771</v>
+        <v>44.26098225879073</v>
       </c>
       <c r="O5" t="n">
-        <v>6.674007615254698</v>
+        <v>6.652892773733147</v>
       </c>
       <c r="P5" t="n">
-        <v>299.4727755553242</v>
+        <v>299.5262572135073</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -28576,28 +28813,28 @@
         <v>0.1324</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3924340401247038</v>
+        <v>0.3807093222963804</v>
       </c>
       <c r="J6" t="n">
+        <v>351</v>
+      </c>
+      <c r="K6" t="n">
         <v>348</v>
       </c>
-      <c r="K6" t="n">
-        <v>345</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.05234956417844527</v>
+        <v>0.05022623528271297</v>
       </c>
       <c r="M6" t="n">
-        <v>9.972579003476046</v>
+        <v>9.92582487031371</v>
       </c>
       <c r="N6" t="n">
-        <v>153.3107834756979</v>
+        <v>151.9392295472369</v>
       </c>
       <c r="O6" t="n">
-        <v>12.38187318121527</v>
+        <v>12.32636319224924</v>
       </c>
       <c r="P6" t="n">
-        <v>288.6330942862123</v>
+        <v>288.7607281662707</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28654,28 +28891,28 @@
         <v>0.1253</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4007152580975858</v>
+        <v>0.416220012213726</v>
       </c>
       <c r="J7" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K7" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1205539952305736</v>
+        <v>0.1292859921781757</v>
       </c>
       <c r="M7" t="n">
-        <v>5.855802458244073</v>
+        <v>5.885882070795877</v>
       </c>
       <c r="N7" t="n">
-        <v>65.10933104912644</v>
+        <v>65.37415288039334</v>
       </c>
       <c r="O7" t="n">
-        <v>8.069035323328709</v>
+        <v>8.085428428994554</v>
       </c>
       <c r="P7" t="n">
-        <v>302.7373961732261</v>
+        <v>302.5698592131189</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28732,28 +28969,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2557189286532476</v>
+        <v>0.273244901061108</v>
       </c>
       <c r="J8" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K8" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06645498693457419</v>
+        <v>0.07493006617741949</v>
       </c>
       <c r="M8" t="n">
-        <v>5.477151687418471</v>
+        <v>5.512035838194241</v>
       </c>
       <c r="N8" t="n">
-        <v>51.02350221387182</v>
+        <v>51.61222708278169</v>
       </c>
       <c r="O8" t="n">
-        <v>7.143073723116109</v>
+        <v>7.184165023353911</v>
       </c>
       <c r="P8" t="n">
-        <v>312.2914160669099</v>
+        <v>312.1019181663985</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28810,28 +29047,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3032703267434003</v>
+        <v>0.3218421679301987</v>
       </c>
       <c r="J9" t="n">
+        <v>351</v>
+      </c>
+      <c r="K9" t="n">
         <v>348</v>
       </c>
-      <c r="K9" t="n">
-        <v>345</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.05683873718323629</v>
+        <v>0.06373080685552091</v>
       </c>
       <c r="M9" t="n">
-        <v>6.940550718244529</v>
+        <v>6.974924606708959</v>
       </c>
       <c r="N9" t="n">
-        <v>85.09694772334595</v>
+        <v>85.52649304929129</v>
       </c>
       <c r="O9" t="n">
-        <v>9.224800687459103</v>
+        <v>9.248053473531135</v>
       </c>
       <c r="P9" t="n">
-        <v>316.0527391102656</v>
+        <v>315.8520838615591</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28888,28 +29125,28 @@
         <v>0.1406</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5216315127914527</v>
+        <v>0.5344148667388078</v>
       </c>
       <c r="J10" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K10" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1805358620057554</v>
+        <v>0.1891440560409777</v>
       </c>
       <c r="M10" t="n">
-        <v>6.465694183677902</v>
+        <v>6.482826113406264</v>
       </c>
       <c r="N10" t="n">
-        <v>67.83949890068729</v>
+        <v>67.79243530999727</v>
       </c>
       <c r="O10" t="n">
-        <v>8.236473693316047</v>
+        <v>8.233616174561289</v>
       </c>
       <c r="P10" t="n">
-        <v>320.3035420049957</v>
+        <v>320.1640272686423</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28966,28 +29203,28 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3664626411983748</v>
+        <v>0.3750406441336632</v>
       </c>
       <c r="J11" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K11" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09019503606668211</v>
+        <v>0.09517850465348232</v>
       </c>
       <c r="M11" t="n">
-        <v>6.261153775054598</v>
+        <v>6.252337372769247</v>
       </c>
       <c r="N11" t="n">
-        <v>75.37291552164557</v>
+        <v>75.00037085363142</v>
       </c>
       <c r="O11" t="n">
-        <v>8.681757628593738</v>
+        <v>8.660275449062311</v>
       </c>
       <c r="P11" t="n">
-        <v>330.6610941526169</v>
+        <v>330.5684878810541</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29044,28 +29281,28 @@
         <v>0.1507</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3985288099092645</v>
+        <v>0.4057245186260796</v>
       </c>
       <c r="J12" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K12" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1018143647834399</v>
+        <v>0.1064565633561156</v>
       </c>
       <c r="M12" t="n">
-        <v>6.870188859504426</v>
+        <v>6.849276008409679</v>
       </c>
       <c r="N12" t="n">
-        <v>77.80485763797427</v>
+        <v>77.34804151629993</v>
       </c>
       <c r="O12" t="n">
-        <v>8.82070618703368</v>
+        <v>8.794773534111036</v>
       </c>
       <c r="P12" t="n">
-        <v>330.3254900559648</v>
+        <v>330.247780747607</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29122,28 +29359,28 @@
         <v>0.1363</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2830661400871027</v>
+        <v>0.2954702261070624</v>
       </c>
       <c r="J13" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K13" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04809696487334025</v>
+        <v>0.05271852444407077</v>
       </c>
       <c r="M13" t="n">
-        <v>7.741333610078958</v>
+        <v>7.738883750019997</v>
       </c>
       <c r="N13" t="n">
-        <v>86.77515597221281</v>
+        <v>86.53965205148796</v>
       </c>
       <c r="O13" t="n">
-        <v>9.315318350556399</v>
+        <v>9.302669082123042</v>
       </c>
       <c r="P13" t="n">
-        <v>333.4585981089913</v>
+        <v>333.3231463745201</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29200,28 +29437,28 @@
         <v>0.0713</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5116982205847179</v>
+        <v>0.5271426207391817</v>
       </c>
       <c r="J14" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K14" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1517210393422203</v>
+        <v>0.160433650531318</v>
       </c>
       <c r="M14" t="n">
-        <v>7.188116587925339</v>
+        <v>7.20659132188322</v>
       </c>
       <c r="N14" t="n">
-        <v>81.29258218556609</v>
+        <v>81.40656088305523</v>
       </c>
       <c r="O14" t="n">
-        <v>9.0162399139312</v>
+        <v>9.022558444424465</v>
       </c>
       <c r="P14" t="n">
-        <v>334.8321739397539</v>
+        <v>334.6653391081236</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29278,28 +29515,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4498052023102033</v>
+        <v>0.4603752756028252</v>
       </c>
       <c r="J15" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K15" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1161684629629215</v>
+        <v>0.1223370781409671</v>
       </c>
       <c r="M15" t="n">
-        <v>7.244622715592608</v>
+        <v>7.235309161015676</v>
       </c>
       <c r="N15" t="n">
-        <v>85.47919386392778</v>
+        <v>85.12109830852864</v>
       </c>
       <c r="O15" t="n">
-        <v>9.245495869012531</v>
+        <v>9.226109597686808</v>
       </c>
       <c r="P15" t="n">
-        <v>337.5412301817866</v>
+        <v>337.427036204712</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29356,28 +29593,28 @@
         <v>0.079</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2776816281223002</v>
+        <v>0.2883098349850709</v>
       </c>
       <c r="J16" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K16" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L16" t="n">
-        <v>0.03940738559330037</v>
+        <v>0.04288362560636927</v>
       </c>
       <c r="M16" t="n">
-        <v>8.188904709011007</v>
+        <v>8.174546493964213</v>
       </c>
       <c r="N16" t="n">
-        <v>104.3725112049456</v>
+        <v>103.8569950717613</v>
       </c>
       <c r="O16" t="n">
-        <v>10.21628656630899</v>
+        <v>10.1910252218195</v>
       </c>
       <c r="P16" t="n">
-        <v>342.8905167609274</v>
+        <v>342.7756925485241</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29434,28 +29671,28 @@
         <v>0.1836</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3671937216867872</v>
+        <v>0.389169473974572</v>
       </c>
       <c r="J17" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K17" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04910578985199232</v>
+        <v>0.05511336606934569</v>
       </c>
       <c r="M17" t="n">
-        <v>9.962959953087566</v>
+        <v>9.998484146646179</v>
       </c>
       <c r="N17" t="n">
-        <v>145.2714363505476</v>
+        <v>145.6407849121051</v>
       </c>
       <c r="O17" t="n">
-        <v>12.05286009005944</v>
+        <v>12.06817239320458</v>
       </c>
       <c r="P17" t="n">
-        <v>341.4129807523034</v>
+        <v>341.1756660644053</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29512,28 +29749,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4938529203951524</v>
+        <v>0.5150877066807635</v>
       </c>
       <c r="J18" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K18" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="L18" t="n">
-        <v>0.07089530762496898</v>
+        <v>0.077251103226601</v>
       </c>
       <c r="M18" t="n">
-        <v>10.00993004672052</v>
+        <v>10.02672573576278</v>
       </c>
       <c r="N18" t="n">
-        <v>170.055891248094</v>
+        <v>169.9973607807251</v>
       </c>
       <c r="O18" t="n">
-        <v>13.04054796579093</v>
+        <v>13.03830360057339</v>
       </c>
       <c r="P18" t="n">
-        <v>336.0259689709895</v>
+        <v>335.7893265516915</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -29594,28 +29831,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.698949546551924</v>
+        <v>1.662959043495821</v>
       </c>
       <c r="J19" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K19" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1446005961396599</v>
+        <v>0.1407776721468719</v>
       </c>
       <c r="M19" t="n">
-        <v>26.34665997894334</v>
+        <v>26.35985264682578</v>
       </c>
       <c r="N19" t="n">
-        <v>939.2923879715449</v>
+        <v>935.8844231114266</v>
       </c>
       <c r="O19" t="n">
-        <v>30.64787738117511</v>
+        <v>30.59222814885223</v>
       </c>
       <c r="P19" t="n">
-        <v>285.4270136562607</v>
+        <v>285.8200714382619</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -29676,28 +29913,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9647459415091267</v>
+        <v>0.9399196730807893</v>
       </c>
       <c r="J20" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K20" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L20" t="n">
-        <v>0.06175195058756178</v>
+        <v>0.05966796647330364</v>
       </c>
       <c r="M20" t="n">
-        <v>23.67931641251078</v>
+        <v>23.56660622001113</v>
       </c>
       <c r="N20" t="n">
-        <v>773.86296897556</v>
+        <v>768.0293332361975</v>
       </c>
       <c r="O20" t="n">
-        <v>27.81839263824493</v>
+        <v>27.71334215204289</v>
       </c>
       <c r="P20" t="n">
-        <v>286.1832769376821</v>
+        <v>286.4546884281954</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -29739,7 +29976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U349"/>
+  <dimension ref="A1:U352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66878,7 +67115,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>-38.46089205304248,174.6443260160573</t>
+          <t>-38.460890533311684,174.6444050600044</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -66948,10 +67185,331 @@
       </c>
       <c r="T349" t="inlineStr">
         <is>
-          <t>-38.45106329105561,174.64302003453517</t>
+          <t>-38.45103534479687,174.64313928021636</t>
         </is>
       </c>
       <c r="U349" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>-38.46371311650855,174.6439710020777</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>-38.463003878022455,174.6442669399068</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>-38.4622975351215,174.64441188337736</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>-38.461593766727695,174.64442256234793</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>-38.46088919634502,174.64447459576226</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-38.46019145118132,174.64417127729556</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>-38.45948902101461,174.64411127766115</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>-38.45878680195934,174.64403993820656</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>-38.45808435193579,174.6439492503711</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>-38.457380809887496,174.643854124509</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>-38.4566772409184,174.64379201889898</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>-38.45597678678686,174.6437092514563</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>-38.45528227260908,174.64353340694873</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>-38.45457773320923,174.64351436722447</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>-38.4538762953594,174.6434466760711</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>-38.45318504407344,174.64329603445015</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>-38.452502830827505,174.64313541742465</t>
+        </is>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>-38.45171373874903,174.64337770944547</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>-38.45101429495772,174.64322909872314</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>-38.46371271350661,174.64399196672855</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>-38.46300306090229,174.64430944158934</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>-38.462296572581046,174.64446194551348</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-38.46159305749115,174.64445944987924</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>-38.46088747386591,174.64456417889073</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-38.46019085435315,174.64420232179523</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-38.45948927206791,174.6440982184773</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>-38.45878710585399,174.64402412987343</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>-38.458084401335114,174.6439470741388</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>-38.457379146729664,174.6438910750229</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>-38.45667457754422,174.64383370468758</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>-38.455975239859264,174.64373346324453</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>-38.45528035358695,174.64356344298895</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>-38.45457747053044,174.64351847858183</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>-38.45387652884947,174.64344302156633</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>-38.45318624308229,174.64328595160032</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>-38.452502036514744,174.64313929833494</t>
+        </is>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>-38.451680285221606,174.6435204540144</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>-38.450982153935605,174.6433662420349</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:12+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>-38.46371275975294,174.64398956094897</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>-38.463003005839724,174.64431230558407</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>-38.46229624218466,174.64447912931263</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-38.46159313238003,174.6444555549226</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>-38.46088708839127,174.6445842262651</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>-38.460190662749746,174.64421228811045</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-38.45948918838365,174.64410257153858</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-38.45878722256659,174.644018058557</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>-38.45808467433063,174.64393504759178</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>-38.457378662712514,174.64390182842286</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>-38.456673767583666,174.64384638173493</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>-38.45597540038972,174.64373095070053</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>-38.45528022954343,174.64356538448197</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>-38.45457791562496,174.6435115121152</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>-38.453876733153194,174.64343982387464</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>-38.45318606794621,174.64328742437615</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>-38.45250037980482,174.64314739280476</t>
+        </is>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>-38.45166988885975,174.64356481460626</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>-38.450975257362614,174.64339566908603</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0259/nzd0259.xlsx
+++ b/data/nzd0259/nzd0259.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U352"/>
+  <dimension ref="A1:U353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24690,6 +24690,75 @@
       <c r="U352" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>345.59</v>
+      </c>
+      <c r="C353" t="n">
+        <v>315.79</v>
+      </c>
+      <c r="D353" t="n">
+        <v>299.24</v>
+      </c>
+      <c r="E353" t="n">
+        <v>302.36</v>
+      </c>
+      <c r="F353" t="n">
+        <v>292.52</v>
+      </c>
+      <c r="G353" t="n">
+        <v>323.44</v>
+      </c>
+      <c r="H353" t="n">
+        <v>331.03</v>
+      </c>
+      <c r="I353" t="n">
+        <v>339.33</v>
+      </c>
+      <c r="J353" t="n">
+        <v>346.19</v>
+      </c>
+      <c r="K353" t="n">
+        <v>345.22</v>
+      </c>
+      <c r="L353" t="n">
+        <v>343.51</v>
+      </c>
+      <c r="M353" t="n">
+        <v>352.1</v>
+      </c>
+      <c r="N353" t="n">
+        <v>355.84</v>
+      </c>
+      <c r="O353" t="n">
+        <v>357.55</v>
+      </c>
+      <c r="P353" t="n">
+        <v>359.38</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>366.41</v>
+      </c>
+      <c r="R353" t="n">
+        <v>362</v>
+      </c>
+      <c r="S353" t="n">
+        <v>301.05</v>
+      </c>
+      <c r="T353" t="n">
+        <v>289.08</v>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -24704,7 +24773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B361"/>
+  <dimension ref="A1:B362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28317,6 +28386,16 @@
       </c>
       <c r="B361" t="n">
         <v>1.01</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>-0.84</v>
       </c>
     </row>
   </sheetData>
@@ -28485,28 +28564,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06650894294160994</v>
+        <v>-0.06656925262853113</v>
       </c>
       <c r="J2" t="n">
+        <v>352</v>
+      </c>
+      <c r="K2" t="n">
         <v>351</v>
       </c>
-      <c r="K2" t="n">
-        <v>350</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.007487008001907269</v>
+        <v>0.007541334891781104</v>
       </c>
       <c r="M2" t="n">
-        <v>3.956936583297106</v>
+        <v>3.945978688594278</v>
       </c>
       <c r="N2" t="n">
-        <v>32.83356277660118</v>
+        <v>32.7400570694757</v>
       </c>
       <c r="O2" t="n">
-        <v>5.730057833617492</v>
+        <v>5.721892787310481</v>
       </c>
       <c r="P2" t="n">
-        <v>347.4796852215981</v>
+        <v>347.4803386760234</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -28567,28 +28646,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05064519461103183</v>
+        <v>-0.05341768628445182</v>
       </c>
       <c r="J3" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K3" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005437486656034829</v>
+        <v>0.006060379134098404</v>
       </c>
       <c r="M3" t="n">
-        <v>4.196570535289176</v>
+        <v>4.197552560849612</v>
       </c>
       <c r="N3" t="n">
-        <v>26.26358199936946</v>
+        <v>26.26748177955926</v>
       </c>
       <c r="O3" t="n">
-        <v>5.124800678989327</v>
+        <v>5.125181146023939</v>
       </c>
       <c r="P3" t="n">
-        <v>322.4217181706482</v>
+        <v>322.4517335294998</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -28649,28 +28728,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02405919838711195</v>
+        <v>0.02192429867677151</v>
       </c>
       <c r="J4" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K4" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005824965417772221</v>
+        <v>0.0004860040744144589</v>
       </c>
       <c r="M4" t="n">
-        <v>5.979926042823185</v>
+        <v>5.972927622137371</v>
       </c>
       <c r="N4" t="n">
-        <v>55.5980415528995</v>
+        <v>55.48664600962286</v>
       </c>
       <c r="O4" t="n">
-        <v>7.456409427660172</v>
+        <v>7.448935897805999</v>
       </c>
       <c r="P4" t="n">
-        <v>302.6656869230369</v>
+        <v>302.6887996275879</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -28731,28 +28810,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2570187788056412</v>
+        <v>0.2549171633929456</v>
       </c>
       <c r="J5" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K5" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07710860525317353</v>
+        <v>0.07626162150266624</v>
       </c>
       <c r="M5" t="n">
-        <v>4.727730979539018</v>
+        <v>4.725663610415999</v>
       </c>
       <c r="N5" t="n">
-        <v>44.26098225879073</v>
+        <v>44.18035399684464</v>
       </c>
       <c r="O5" t="n">
-        <v>6.652892773733147</v>
+        <v>6.646830372203329</v>
       </c>
       <c r="P5" t="n">
-        <v>299.5262572135073</v>
+        <v>299.5490095778823</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -28813,28 +28892,28 @@
         <v>0.1324</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3807093222963804</v>
+        <v>0.3773300708474603</v>
       </c>
       <c r="J6" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K6" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05022623528271297</v>
+        <v>0.04960466739475644</v>
       </c>
       <c r="M6" t="n">
-        <v>9.92582487031371</v>
+        <v>9.918686903833887</v>
       </c>
       <c r="N6" t="n">
-        <v>151.9392295472369</v>
+        <v>151.6192494870857</v>
       </c>
       <c r="O6" t="n">
-        <v>12.32636319224924</v>
+        <v>12.3133768515012</v>
       </c>
       <c r="P6" t="n">
-        <v>288.7607281662707</v>
+        <v>288.7976357033637</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28891,28 +28970,28 @@
         <v>0.1253</v>
       </c>
       <c r="I7" t="n">
-        <v>0.416220012213726</v>
+        <v>0.4213642913061029</v>
       </c>
       <c r="J7" t="n">
+        <v>352</v>
+      </c>
+      <c r="K7" t="n">
         <v>351</v>
       </c>
-      <c r="K7" t="n">
-        <v>350</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1292859921781757</v>
+        <v>0.1322287957110143</v>
       </c>
       <c r="M7" t="n">
-        <v>5.885882070795877</v>
+        <v>5.895786916626583</v>
       </c>
       <c r="N7" t="n">
-        <v>65.37415288039334</v>
+        <v>65.45883524555066</v>
       </c>
       <c r="O7" t="n">
-        <v>8.085428428994554</v>
+        <v>8.090663461394909</v>
       </c>
       <c r="P7" t="n">
-        <v>302.5698592131189</v>
+        <v>302.5141478637514</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28969,28 +29048,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.273244901061108</v>
+        <v>0.2793699375882223</v>
       </c>
       <c r="J8" t="n">
+        <v>352</v>
+      </c>
+      <c r="K8" t="n">
         <v>351</v>
       </c>
-      <c r="K8" t="n">
-        <v>350</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.07493006617741949</v>
+        <v>0.07792114407990658</v>
       </c>
       <c r="M8" t="n">
-        <v>5.512035838194241</v>
+        <v>5.52472074489055</v>
       </c>
       <c r="N8" t="n">
-        <v>51.61222708278169</v>
+        <v>51.84894852436745</v>
       </c>
       <c r="O8" t="n">
-        <v>7.184165023353911</v>
+        <v>7.200621398488289</v>
       </c>
       <c r="P8" t="n">
-        <v>312.1019181663985</v>
+        <v>312.0355535004823</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29047,28 +29126,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3218421679301987</v>
+        <v>0.3296782743087771</v>
       </c>
       <c r="J9" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K9" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06373080685552091</v>
+        <v>0.06654261892890434</v>
       </c>
       <c r="M9" t="n">
-        <v>6.974924606708959</v>
+        <v>6.994844825173245</v>
       </c>
       <c r="N9" t="n">
-        <v>85.52649304929129</v>
+        <v>85.91373563243341</v>
       </c>
       <c r="O9" t="n">
-        <v>9.248053473531135</v>
+        <v>9.268966265578563</v>
       </c>
       <c r="P9" t="n">
-        <v>315.8520838615591</v>
+        <v>315.7672448277675</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29125,28 +29204,28 @@
         <v>0.1406</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5344148667388078</v>
+        <v>0.5406875793456244</v>
       </c>
       <c r="J10" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K10" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1891440560409777</v>
+        <v>0.1926932642771917</v>
       </c>
       <c r="M10" t="n">
-        <v>6.482826113406264</v>
+        <v>6.500728613216688</v>
       </c>
       <c r="N10" t="n">
-        <v>67.79243530999727</v>
+        <v>67.99435436647747</v>
       </c>
       <c r="O10" t="n">
-        <v>8.233616174561289</v>
+        <v>8.245868927316119</v>
       </c>
       <c r="P10" t="n">
-        <v>320.1640272686423</v>
+        <v>320.0954278994132</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29203,28 +29282,28 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3750406441336632</v>
+        <v>0.3774937432267266</v>
       </c>
       <c r="J11" t="n">
+        <v>352</v>
+      </c>
+      <c r="K11" t="n">
         <v>351</v>
       </c>
-      <c r="K11" t="n">
-        <v>350</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.09517850465348232</v>
+        <v>0.09671268069812811</v>
       </c>
       <c r="M11" t="n">
-        <v>6.252337372769247</v>
+        <v>6.247449052385076</v>
       </c>
       <c r="N11" t="n">
-        <v>75.00037085363142</v>
+        <v>74.84836490070434</v>
       </c>
       <c r="O11" t="n">
-        <v>8.660275449062311</v>
+        <v>8.651494951781705</v>
       </c>
       <c r="P11" t="n">
-        <v>330.5684878810541</v>
+        <v>330.5419415011573</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29281,28 +29360,28 @@
         <v>0.1507</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4057245186260796</v>
+        <v>0.4070209409902102</v>
       </c>
       <c r="J12" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K12" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1064565633561156</v>
+        <v>0.1075687086861363</v>
       </c>
       <c r="M12" t="n">
-        <v>6.849276008409679</v>
+        <v>6.83657452489497</v>
       </c>
       <c r="N12" t="n">
-        <v>77.34804151629993</v>
+        <v>77.14546958127123</v>
       </c>
       <c r="O12" t="n">
-        <v>8.794773534111036</v>
+        <v>8.783249374876659</v>
       </c>
       <c r="P12" t="n">
-        <v>330.247780747607</v>
+        <v>330.233745508888</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29359,28 +29438,28 @@
         <v>0.1363</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2954702261070624</v>
+        <v>0.3012752379777708</v>
       </c>
       <c r="J13" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K13" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05271852444407077</v>
+        <v>0.0547788776348479</v>
       </c>
       <c r="M13" t="n">
-        <v>7.738883750019997</v>
+        <v>7.746572890184839</v>
       </c>
       <c r="N13" t="n">
-        <v>86.53965205148796</v>
+        <v>86.62994072599125</v>
       </c>
       <c r="O13" t="n">
-        <v>9.302669082123042</v>
+        <v>9.307520654072773</v>
       </c>
       <c r="P13" t="n">
-        <v>333.3231463745201</v>
+        <v>333.2596184570814</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29437,28 +29516,28 @@
         <v>0.0713</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5271426207391817</v>
+        <v>0.5308941342061866</v>
       </c>
       <c r="J14" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K14" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L14" t="n">
-        <v>0.160433650531318</v>
+        <v>0.1628585380965893</v>
       </c>
       <c r="M14" t="n">
-        <v>7.20659132188322</v>
+        <v>7.205541254607562</v>
       </c>
       <c r="N14" t="n">
-        <v>81.40656088305523</v>
+        <v>81.31904289719391</v>
       </c>
       <c r="O14" t="n">
-        <v>9.022558444424465</v>
+        <v>9.017707186263808</v>
       </c>
       <c r="P14" t="n">
-        <v>334.6653391081236</v>
+        <v>334.6247247308008</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29515,28 +29594,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4603752756028252</v>
+        <v>0.4645114660335471</v>
       </c>
       <c r="J15" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K15" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1223370781409671</v>
+        <v>0.1246438633203654</v>
       </c>
       <c r="M15" t="n">
-        <v>7.235309161015676</v>
+        <v>7.235328404993452</v>
       </c>
       <c r="N15" t="n">
-        <v>85.12109830852864</v>
+        <v>85.05401923005066</v>
       </c>
       <c r="O15" t="n">
-        <v>9.226109597686808</v>
+        <v>9.222473596061452</v>
       </c>
       <c r="P15" t="n">
-        <v>337.427036204712</v>
+        <v>337.3822572640764</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29593,28 +29672,28 @@
         <v>0.079</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2883098349850709</v>
+        <v>0.2930018593536718</v>
       </c>
       <c r="J16" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K16" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L16" t="n">
-        <v>0.04288362560636927</v>
+        <v>0.04436873296513755</v>
       </c>
       <c r="M16" t="n">
-        <v>8.174546493964213</v>
+        <v>8.17607489589161</v>
       </c>
       <c r="N16" t="n">
-        <v>103.8569950717613</v>
+        <v>103.7868094403788</v>
       </c>
       <c r="O16" t="n">
-        <v>10.1910252218195</v>
+        <v>10.18758113785499</v>
       </c>
       <c r="P16" t="n">
-        <v>342.7756925485241</v>
+        <v>342.7248960767027</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29671,28 +29750,28 @@
         <v>0.1836</v>
       </c>
       <c r="I17" t="n">
-        <v>0.389169473974572</v>
+        <v>0.3969792260116357</v>
       </c>
       <c r="J17" t="n">
+        <v>352</v>
+      </c>
+      <c r="K17" t="n">
         <v>351</v>
       </c>
-      <c r="K17" t="n">
-        <v>350</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.05511336606934569</v>
+        <v>0.05728328668647698</v>
       </c>
       <c r="M17" t="n">
-        <v>9.998484146646179</v>
+        <v>10.01316595850049</v>
       </c>
       <c r="N17" t="n">
-        <v>145.6407849121051</v>
+        <v>145.8509121475105</v>
       </c>
       <c r="O17" t="n">
-        <v>12.06817239320458</v>
+        <v>12.07687509861349</v>
       </c>
       <c r="P17" t="n">
-        <v>341.1756660644053</v>
+        <v>341.0911522976923</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29749,28 +29828,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5150877066807635</v>
+        <v>0.5219039025285331</v>
       </c>
       <c r="J18" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K18" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L18" t="n">
-        <v>0.077251103226601</v>
+        <v>0.07935906354676914</v>
       </c>
       <c r="M18" t="n">
-        <v>10.02672573576278</v>
+        <v>10.03104660657782</v>
       </c>
       <c r="N18" t="n">
-        <v>169.9973607807251</v>
+        <v>169.9544158878369</v>
       </c>
       <c r="O18" t="n">
-        <v>13.03830360057339</v>
+        <v>13.03665662230301</v>
       </c>
       <c r="P18" t="n">
-        <v>335.7893265516915</v>
+        <v>335.7132084852621</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -29831,28 +29910,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.662959043495821</v>
+        <v>1.64754861386682</v>
       </c>
       <c r="J19" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K19" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1407776721468719</v>
+        <v>0.1388862300178468</v>
       </c>
       <c r="M19" t="n">
-        <v>26.35985264682578</v>
+        <v>26.3870597617502</v>
       </c>
       <c r="N19" t="n">
-        <v>935.8844231114266</v>
+        <v>935.5941527325225</v>
       </c>
       <c r="O19" t="n">
-        <v>30.59222814885223</v>
+        <v>30.5874835959502</v>
       </c>
       <c r="P19" t="n">
-        <v>285.8200714382619</v>
+        <v>285.9886819533571</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -29913,28 +29992,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9399196730807893</v>
+        <v>0.927993001737752</v>
       </c>
       <c r="J20" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K20" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05966796647330364</v>
+        <v>0.0584502720347938</v>
       </c>
       <c r="M20" t="n">
-        <v>23.56660622001113</v>
+        <v>23.57325589769471</v>
       </c>
       <c r="N20" t="n">
-        <v>768.0293332361975</v>
+        <v>767.2511215273677</v>
       </c>
       <c r="O20" t="n">
-        <v>27.71334215204289</v>
+        <v>27.6992982136257</v>
       </c>
       <c r="P20" t="n">
-        <v>286.4546884281954</v>
+        <v>286.5854654697982</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -29976,7 +30055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U352"/>
+  <dimension ref="A1:U353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67515,6 +67594,113 @@
         </is>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>-38.46371264083373,174.64399574723933</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>-38.46300274814601,174.6443257090793</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-38.462295766409426,174.6445038739829</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-38.46159311035391,174.64445670049807</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-38.46088759281168,174.64455799284372</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-38.46019104595571,174.64419235547993</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-38.45948935354983,174.64409397997022</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-38.45878781052908,174.64398747286822</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>-38.458085527108615,174.64389747894884</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>-38.457379229115475,174.64388924465695</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>-38.456673767583666,174.64384638173493</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>-38.45597827533515,174.64368595331928</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>-38.45527923719413,174.6435809164259</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>-38.45457871095673,174.64349906383853</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>-38.45387826542833,174.64341584118623</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>-38.45318760375422,174.64327450926467</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>-38.45250155992699,174.64314162688112</t>
+        </is>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>-38.45166988885975,174.64356481460626</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>-38.450962647937985,174.64344947226144</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
